--- a/output/Data and Chart Outputs/south_america_prices_vs_hydro.xlsx
+++ b/output/Data and Chart Outputs/south_america_prices_vs_hydro.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Chile" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Uruguay" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Peru" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Colombia" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Brazil" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brazil" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Colombia" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peru" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uruguay" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chile" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chart - Chile" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Chart - Uruguay" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Chart - Peru" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Chart - Colombia" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Chart - Brazil" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Brazil" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Colombia" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Peru" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Uruguay" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Chile" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -152,13 +152,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -182,7 +182,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="2A78D6"/>
               </a:solidFill>
@@ -192,7 +192,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -224,8 +224,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -251,8 +251,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -269,7 +269,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -279,7 +279,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -288,13 +288,13 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -318,7 +318,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="2A78D6"/>
               </a:solidFill>
@@ -328,7 +328,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -360,8 +360,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -389,8 +389,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -408,7 +408,7 @@
         <majorUnit val="20"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -418,7 +418,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -427,13 +427,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -457,7 +457,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="2A78D6"/>
               </a:solidFill>
@@ -467,7 +467,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -499,8 +499,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -528,8 +528,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -547,7 +547,7 @@
         <majorUnit val="20"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -557,7 +557,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -566,13 +566,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -596,7 +596,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="2A78D6"/>
               </a:solidFill>
@@ -606,7 +606,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -638,8 +638,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -665,8 +665,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -683,7 +683,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -693,7 +693,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -702,13 +702,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -732,7 +732,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="2A78D6"/>
               </a:solidFill>
@@ -742,7 +742,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -774,8 +774,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -803,8 +803,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -822,7 +822,7 @@
         <majorUnit val="20"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -832,7 +832,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -841,13 +841,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -871,7 +871,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="2A78D6"/>
               </a:solidFill>
@@ -881,7 +881,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -913,8 +913,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -940,8 +940,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -958,7 +958,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -968,7 +968,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -977,13 +977,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1007,7 +1007,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="2A78D6"/>
               </a:solidFill>
@@ -1017,7 +1017,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1049,8 +1049,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1078,8 +1078,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1097,7 +1097,7 @@
         <majorUnit val="20"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1107,7 +1107,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1116,18 +1116,18 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Colombia: wholesale power price (to Sep/26)</a:t>
+              <a:t>Colombia: wholesale power price (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1146,7 +1146,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="2A78D6"/>
               </a:solidFill>
@@ -1156,19 +1156,19 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Colombia'!$A$2:$A$70</f>
+              <f>'Chart - Colombia'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Colombia'!$B$2:$B$70</f>
+              <f>'Chart - Colombia'!$B$2:$B$71</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1188,8 +1188,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1215,8 +1215,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1233,7 +1233,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1243,7 +1243,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1252,18 +1252,18 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Colombia: hydro storage (to Sep/26)</a:t>
+              <a:t>Colombia: hydro storage (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1282,7 +1282,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="2A78D6"/>
               </a:solidFill>
@@ -1292,19 +1292,19 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Colombia'!$D$2:$D$70</f>
+              <f>'Chart - Colombia'!$D$2:$D$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Colombia'!$E$2:$E$70</f>
+              <f>'Chart - Colombia'!$E$2:$E$71</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1324,8 +1324,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1353,8 +1353,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1372,7 +1372,7 @@
         <majorUnit val="20"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1382,7 +1382,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1391,13 +1391,13 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1421,7 +1421,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="2A78D6"/>
               </a:solidFill>
@@ -1431,7 +1431,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1463,8 +1463,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1490,8 +1490,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1508,7 +1508,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1518,7 +1518,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1527,7 +1527,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -1542,9 +1542,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1564,9 +1564,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1576,7 +1576,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -1591,9 +1591,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1613,9 +1613,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1625,7 +1625,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -1640,9 +1640,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1662,9 +1662,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1674,7 +1674,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -1689,9 +1689,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1711,9 +1711,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1723,7 +1723,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -1738,9 +1738,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1760,9 +1760,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2112,7 +2112,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Colombia: price = XM Precio de Bolsa (monthly mean of daily US$/MWh); storage = XM useful stored energy (% of capacity) (monthly mean). Jan-21 to Sep-26.</t>
+          <t>Colombia: price = XM Precio de Bolsa (monthly mean of daily US$/MWh); storage = XM useful stored energy (% of capacity) (monthly mean). Jan-21 to Oct-26.</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
         <v>46296</v>
       </c>
       <c r="C71" t="n">
-        <v>94.3</v>
+        <v>94.34999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3700,7 +3700,7 @@
         <v>46296</v>
       </c>
       <c r="C71" t="n">
-        <v>52.74</v>
+        <v>52.76</v>
       </c>
     </row>
   </sheetData>
@@ -4675,7 +4675,7 @@
         <v>46296</v>
       </c>
       <c r="E71" t="n">
-        <v>52.74</v>
+        <v>52.76</v>
       </c>
     </row>
   </sheetData>
@@ -5690,7 +5690,7 @@
         <v>46296</v>
       </c>
       <c r="E71" t="n">
-        <v>94.3</v>
+        <v>94.34999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -6425,7 +6425,7 @@
         <v>45689</v>
       </c>
       <c r="B51" t="n">
-        <v>28.64</v>
+        <v>28.46</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>45689</v>
@@ -6439,7 +6439,7 @@
         <v>45717</v>
       </c>
       <c r="B52" t="n">
-        <v>29.46</v>
+        <v>31.76</v>
       </c>
       <c r="D52" s="3" t="n">
         <v>45717</v>
@@ -6453,7 +6453,7 @@
         <v>45748</v>
       </c>
       <c r="B53" t="n">
-        <v>21.24</v>
+        <v>22.03</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>45748</v>
@@ -6467,7 +6467,7 @@
         <v>45778</v>
       </c>
       <c r="B54" t="n">
-        <v>25.04</v>
+        <v>25.21</v>
       </c>
       <c r="D54" s="3" t="n">
         <v>45778</v>
@@ -6481,7 +6481,7 @@
         <v>45809</v>
       </c>
       <c r="B55" t="n">
-        <v>28.47</v>
+        <v>28.44</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>45809</v>
@@ -6509,7 +6509,7 @@
         <v>45870</v>
       </c>
       <c r="B57" t="n">
-        <v>30.34</v>
+        <v>30.26</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>45870</v>
@@ -6523,7 +6523,7 @@
         <v>45901</v>
       </c>
       <c r="B58" t="n">
-        <v>28.18</v>
+        <v>28.73</v>
       </c>
       <c r="D58" s="3" t="n">
         <v>45901</v>
@@ -6537,7 +6537,7 @@
         <v>45931</v>
       </c>
       <c r="B59" t="n">
-        <v>27.14</v>
+        <v>27.08</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>45931</v>
@@ -6565,7 +6565,7 @@
         <v>45992</v>
       </c>
       <c r="B61" t="n">
-        <v>37.46</v>
+        <v>37.44</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>45992</v>
@@ -6712,7 +6712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7704,7 +7704,18 @@
         <v>46266</v>
       </c>
       <c r="E70" t="n">
-        <v>76.09</v>
+        <v>78.36</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E71" t="n">
+        <v>76.12</v>
       </c>
     </row>
   </sheetData>
@@ -8711,7 +8722,7 @@
         <v>46266</v>
       </c>
       <c r="E70" t="n">
-        <v>57.22</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="71">
@@ -8723,6 +8734,9 @@
       </c>
       <c r="D71" s="3" t="n">
         <v>46296</v>
+      </c>
+      <c r="E71" t="n">
+        <v>56.3</v>
       </c>
     </row>
   </sheetData>
@@ -9513,7 +9527,7 @@
         <v>17.07</v>
       </c>
       <c r="C70" t="n">
-        <v>57.22</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="71">
@@ -9522,6 +9536,9 @@
       </c>
       <c r="B71" t="n">
         <v>15.86</v>
+      </c>
+      <c r="C71" t="n">
+        <v>56.3</v>
       </c>
     </row>
   </sheetData>
@@ -9535,7 +9552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10311,7 +10328,15 @@
         <v>212.08</v>
       </c>
       <c r="C70" t="n">
-        <v>76.09</v>
+        <v>78.36</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C71" t="n">
+        <v>76.12</v>
       </c>
     </row>
   </sheetData>
@@ -10889,7 +10914,7 @@
         <v>45689</v>
       </c>
       <c r="B51" t="n">
-        <v>28.64</v>
+        <v>28.46</v>
       </c>
       <c r="C51" t="n">
         <v>73.52</v>
@@ -10900,7 +10925,7 @@
         <v>45717</v>
       </c>
       <c r="B52" t="n">
-        <v>29.46</v>
+        <v>31.76</v>
       </c>
       <c r="C52" t="n">
         <v>93.55</v>
@@ -10911,7 +10936,7 @@
         <v>45748</v>
       </c>
       <c r="B53" t="n">
-        <v>21.24</v>
+        <v>22.03</v>
       </c>
       <c r="C53" t="n">
         <v>97.22</v>
@@ -10922,7 +10947,7 @@
         <v>45778</v>
       </c>
       <c r="B54" t="n">
-        <v>25.04</v>
+        <v>25.21</v>
       </c>
       <c r="C54" t="n">
         <v>96.84</v>
@@ -10933,7 +10958,7 @@
         <v>45809</v>
       </c>
       <c r="B55" t="n">
-        <v>28.47</v>
+        <v>28.44</v>
       </c>
       <c r="C55" t="n">
         <v>93.12</v>
@@ -10955,7 +10980,7 @@
         <v>45870</v>
       </c>
       <c r="B57" t="n">
-        <v>30.34</v>
+        <v>30.26</v>
       </c>
       <c r="C57" t="n">
         <v>78.51000000000001</v>
@@ -10966,7 +10991,7 @@
         <v>45901</v>
       </c>
       <c r="B58" t="n">
-        <v>28.18</v>
+        <v>28.73</v>
       </c>
       <c r="C58" t="n">
         <v>66.79000000000001</v>
@@ -10977,7 +11002,7 @@
         <v>45931</v>
       </c>
       <c r="B59" t="n">
-        <v>27.14</v>
+        <v>27.08</v>
       </c>
       <c r="C59" t="n">
         <v>57.28</v>
@@ -10999,7 +11024,7 @@
         <v>45992</v>
       </c>
       <c r="B61" t="n">
-        <v>37.46</v>
+        <v>37.44</v>
       </c>
       <c r="C61" t="n">
         <v>44.9</v>

--- a/output/Data and Chart Outputs/south_america_prices_vs_hydro.xlsx
+++ b/output/Data and Chart Outputs/south_america_prices_vs_hydro.xlsx
@@ -163,6 +163,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Chile: wholesale power price (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -299,6 +300,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Brazil: hydro storage (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -320,7 +322,7 @@
           <spPr>
             <a:ln w="22225">
               <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
+                <a:srgbClr val="4A3AA7"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -438,6 +440,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Chile: hydro storage (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -459,7 +462,7 @@
           <spPr>
             <a:ln w="22225">
               <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
+                <a:srgbClr val="4A3AA7"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -577,6 +580,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Uruguay: wholesale power price (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -713,6 +717,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Uruguay: hydro storage (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -734,7 +739,7 @@
           <spPr>
             <a:ln w="22225">
               <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
+                <a:srgbClr val="4A3AA7"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -852,7 +857,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Peru: wholesale power price (to Sep/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Peru: wholesale power price (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -888,12 +894,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Peru'!$A$2:$A$70</f>
+              <f>'Chart - Peru'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Peru'!$B$2:$B$70</f>
+              <f>'Chart - Peru'!$B$2:$B$71</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -988,7 +994,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Peru: hydro storage (to Sep/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Peru: hydro storage (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1009,7 +1016,7 @@
           <spPr>
             <a:ln w="22225">
               <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
+                <a:srgbClr val="4A3AA7"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1024,12 +1031,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Peru'!$D$2:$D$70</f>
+              <f>'Chart - Peru'!$D$2:$D$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Peru'!$E$2:$E$70</f>
+              <f>'Chart - Peru'!$E$2:$E$71</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1127,6 +1134,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Colombia: wholesale power price (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -1263,6 +1271,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Colombia: hydro storage (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -1284,7 +1293,7 @@
           <spPr>
             <a:ln w="22225">
               <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
+                <a:srgbClr val="4A3AA7"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1402,6 +1411,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Brazil: wholesale power price (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -2119,7 +2129,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Peru: price = COES marginal cost, Santa Rosa 220 kV (monthly mean of daily US$/MWh); storage = COES reservoirs and lagoons, useful volume (%) (monthly mean). Jan-21 to Sep-26.</t>
+          <t>Peru: price = COES marginal cost, Santa Rosa 220 kV (monthly mean of daily US$/MWh); storage = COES reservoirs and lagoons, useful volume (%) (monthly mean). Jan-21 to Oct-26.</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2954,7 @@
         <v>46296</v>
       </c>
       <c r="C71" t="n">
-        <v>94.34999999999999</v>
+        <v>95.02</v>
       </c>
     </row>
   </sheetData>
@@ -3700,7 +3710,7 @@
         <v>46296</v>
       </c>
       <c r="C71" t="n">
-        <v>52.76</v>
+        <v>54.8</v>
       </c>
     </row>
   </sheetData>
@@ -4675,7 +4685,7 @@
         <v>46296</v>
       </c>
       <c r="E71" t="n">
-        <v>52.76</v>
+        <v>54.8</v>
       </c>
     </row>
   </sheetData>
@@ -5690,7 +5700,7 @@
         <v>46296</v>
       </c>
       <c r="E71" t="n">
-        <v>94.34999999999999</v>
+        <v>95.02</v>
       </c>
     </row>
   </sheetData>
@@ -5705,7 +5715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5745,7 +5755,7 @@
         <v>44197</v>
       </c>
       <c r="E2" t="n">
-        <v>50.52</v>
+        <v>50.53</v>
       </c>
     </row>
     <row r="3">
@@ -6081,7 +6091,7 @@
         <v>44927</v>
       </c>
       <c r="E26" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="27">
@@ -6403,7 +6413,7 @@
         <v>45627</v>
       </c>
       <c r="E49" t="n">
-        <v>44.39</v>
+        <v>44.38</v>
       </c>
     </row>
     <row r="50">
@@ -6697,7 +6707,18 @@
         <v>46266</v>
       </c>
       <c r="E70" t="n">
-        <v>61.78</v>
+        <v>61.83</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E71" t="n">
+        <v>51.83</v>
       </c>
     </row>
   </sheetData>
@@ -7715,7 +7736,7 @@
         <v>46296</v>
       </c>
       <c r="E71" t="n">
-        <v>76.12</v>
+        <v>75.84999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -8722,7 +8743,7 @@
         <v>46266</v>
       </c>
       <c r="E70" t="n">
-        <v>57.2</v>
+        <v>57.21</v>
       </c>
     </row>
     <row r="71">
@@ -8736,7 +8757,7 @@
         <v>46296</v>
       </c>
       <c r="E71" t="n">
-        <v>56.3</v>
+        <v>55.38</v>
       </c>
     </row>
   </sheetData>
@@ -9527,7 +9548,7 @@
         <v>17.07</v>
       </c>
       <c r="C70" t="n">
-        <v>57.2</v>
+        <v>57.21</v>
       </c>
     </row>
     <row r="71">
@@ -9538,7 +9559,7 @@
         <v>15.86</v>
       </c>
       <c r="C71" t="n">
-        <v>56.3</v>
+        <v>55.38</v>
       </c>
     </row>
   </sheetData>
@@ -10336,7 +10357,7 @@
         <v>46296</v>
       </c>
       <c r="C71" t="n">
-        <v>76.12</v>
+        <v>75.84999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -10350,7 +10371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10378,7 +10399,7 @@
         <v>7.11</v>
       </c>
       <c r="C2" t="n">
-        <v>50.52</v>
+        <v>50.53</v>
       </c>
     </row>
     <row r="3">
@@ -10642,7 +10663,7 @@
         <v>31.18</v>
       </c>
       <c r="C26" t="n">
-        <v>31.83</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="27">
@@ -10895,7 +10916,7 @@
         <v>24.44</v>
       </c>
       <c r="C49" t="n">
-        <v>44.39</v>
+        <v>44.38</v>
       </c>
     </row>
     <row r="50">
@@ -11126,7 +11147,15 @@
         <v>118.61</v>
       </c>
       <c r="C70" t="n">
-        <v>61.78</v>
+        <v>61.83</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C71" t="n">
+        <v>51.83</v>
       </c>
     </row>
   </sheetData>
